--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.69012857627932</v>
+        <v>4.662145893645389</v>
       </c>
       <c r="D2" t="n">
-        <v>28.67171976372444</v>
+        <v>4.659154461605223</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F2" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.60177956075297</v>
+        <v>9.847789178622358</v>
       </c>
       <c r="D3" t="n">
-        <v>60.4108734454551</v>
+        <v>9.816766934886454</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F3" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.3229431941163</v>
+        <v>2.652478269043898</v>
       </c>
       <c r="D4" t="n">
-        <v>21.47432645979734</v>
+        <v>3.489578049717069</v>
       </c>
       <c r="E4" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F4" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.77295534706856</v>
+        <v>9.388105243898641</v>
       </c>
       <c r="D5" t="n">
-        <v>57.55455041057745</v>
+        <v>9.352614441718835</v>
       </c>
       <c r="E5" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F5" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.55248793452726</v>
+        <v>3.177279289360679</v>
       </c>
       <c r="D6" t="n">
-        <v>19.48187458281775</v>
+        <v>3.165804619707884</v>
       </c>
       <c r="E6" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F6" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.38795516299699</v>
+        <v>6.88804271398701</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10446840785703</v>
+        <v>6.841976116276768</v>
       </c>
       <c r="E7" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F7" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4880461189103</v>
+        <v>2.516807494322924</v>
       </c>
       <c r="D8" t="n">
-        <v>15.69752395426663</v>
+        <v>2.550847642568327</v>
       </c>
       <c r="E8" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F8" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.40753762821886</v>
+        <v>1.853724864585565</v>
       </c>
       <c r="D9" t="n">
-        <v>42.09581665468507</v>
+        <v>6.840570206386324</v>
       </c>
       <c r="E9" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F9" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.16327457180631</v>
+        <v>3.764032117918525</v>
       </c>
       <c r="D10" t="n">
-        <v>54.61699055150751</v>
+        <v>8.87526096461997</v>
       </c>
       <c r="E10" t="n">
-        <v>17.5086907860859</v>
+        <v>2.845162252738958</v>
       </c>
       <c r="F10" t="n">
-        <v>16.31226275506933</v>
+        <v>2.650742697698766</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
